--- a/reports/pdf_rolling5_20260724.xlsx
+++ b/reports/pdf_rolling5_20260724.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,207억   ·   현금 89억(2.0%)      오늘 2026-07-24  vs  5일전 2026-07-16      매수 14종목  /  매도 18종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,394억   ·   현금 90억(2.0%)      오늘 2026-07-24  vs  5일전 2026-07-16      매수 14종목  /  매도 18종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>344</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1464182680</v>
+        <v>1467137640</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-50</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-627798500</v>
+        <v>-629065500</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>31</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1388589200</v>
+        <v>1391391600</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-39</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1497648750</v>
+        <v>-1500671250</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>27</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>888332400</v>
+        <v>890125200</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-35</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1657943000</v>
+        <v>-1661289000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>25</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1149560000</v>
+        <v>1151880000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-28</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-901810000</v>
+        <v>-903630000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>23</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>366967300</v>
+        <v>367707900</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-26</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-476671000</v>
+        <v>-477633000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>16</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1918576000</v>
+        <v>1922448000</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-23</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-968702500</v>
+        <v>-970657500</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -927,23 +927,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1168983600</v>
+        <v>406931400</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>4.17%→4.03%</t>
+          <t>0.50%→0.61%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>168→180</t>
+          <t>66→78</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -955,7 +955,7 @@
         <v>-20</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-538113000</v>
+        <v>-539199000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -971,23 +971,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>406111800</v>
+        <v>428976000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>0.50%→0.61%</t>
+          <t>0.67%→0.77%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>66→78</t>
+          <t>82→94</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -999,7 +999,7 @@
         <v>-20</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-258452800</v>
+        <v>-258974400</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1015,23 +1015,23 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>428112000</v>
+        <v>1171342800</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>0.67%→0.77%</t>
+          <t>4.17%→4.03%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>82→94</t>
+          <t>168→180</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1043,7 +1043,7 @@
         <v>-16</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-2443409600</v>
+        <v>-2448340800</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>9</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>404922600</v>
+        <v>405739800</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>-15</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-1025685000</v>
+        <v>-1027755000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>8</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1716412000</v>
+        <v>1719876000</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>-14</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-432868800</v>
+        <v>-433742400</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>5</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>777935000</v>
+        <v>779505000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1168,23 +1168,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-394021600</v>
+        <v>-421230600</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.37%→0.27%</t>
+          <t>0.56%→0.48%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>56→42</t>
+          <t>84→70</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
         <v>4</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2013712000</v>
+        <v>2017776000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1212,23 +1212,23 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-420382200</v>
+        <v>-394816800</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.56%→0.48%</t>
+          <t>0.37%→0.27%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>84→70</t>
+          <t>56→42</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
         <v>3</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>712033500</v>
+        <v>713470500</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>-8</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-224758800</v>
+        <v>-225212400</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1284,23 +1284,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-441787800</v>
+        <v>-381312000</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>2.23%→2.23%</t>
+          <t>1.24%→1.08%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>138→132</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>
@@ -1312,23 +1312,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-380544000</v>
+        <v>-442679400</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>1.24%→1.08%</t>
+          <t>2.23%→2.23%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>138→132</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
         <v>-5</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-417706500</v>
+        <v>-418549500</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>-3</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-338327400</v>
+        <v>-339010200</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,697억   ·   현금 42억(1.1%)      오늘 2026-07-24  vs  5일전 2026-07-16      매수 5종목  /  매도 1종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,701억   ·   현금 42억(1.1%)      오늘 2026-07-24  vs  5일전 2026-07-16      매수 5종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1487,7 +1487,7 @@
         <v>46</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1982324000</v>
+        <v>1989159600</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>-138</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-8140068000</v>
+        <v>-8168137200</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>40</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1151880000</v>
+        <v>1155852000</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>17</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>1122068000</v>
+        <v>1125937200</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>12</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>2133240000</v>
+        <v>2140596000</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>5</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>1128100000</v>
+        <v>1131990000</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,423억   ·   현금 109억(4.2%)      오늘 2026-07-24  vs  5일전 2026-07-16      매수 3종목  /  매도 4종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,527억   ·   현금 110억(4.2%)      오늘 2026-07-24  vs  5일전 2026-07-16      매수 3종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B34" s="4" t="n"/>
@@ -1732,7 +1732,7 @@
         <v>148</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>4651566000</v>
+        <v>4685273000</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1746,18 +1746,18 @@
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-1126080000</v>
+        <v>-2278210000</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>4.21%→2.95%</t>
+          <t>7.61%→5.92%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
@@ -1776,7 +1776,7 @@
         <v>25</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>453675000</v>
+        <v>456962500</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1790,23 +1790,23 @@
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H38" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-2126580000</v>
+        <v>-1134240000</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>9.85%→7.28%</t>
+          <t>4.21%→2.95%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>190→170</t>
+          <t>150→130</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
         <v>9</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>3154680000</v>
+        <v>3177540000</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1834,23 +1834,23 @@
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H39" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-2261820000</v>
+        <v>-2141990000</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>7.61%→5.92%</t>
+          <t>9.85%→7.28%</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
         <is>
-          <t>150→130</t>
+          <t>190→170</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
         <v>-19</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-2058270000</v>
+        <v>-2073185000</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
     <row r="42" ht="19" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,183억   ·   현금 73억(3.1%)      오늘 2026-07-24  vs  5일전 2026-07-16      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,244억   ·   현금 73억(3.1%)      오늘 2026-07-24  vs  5일전 2026-07-16      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B42" s="4" t="n"/>
@@ -1909,7 +1909,7 @@
     <row r="45" ht="19" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 274억   ·   현금 1억(0.5%)      오늘 2026-07-24  vs  5일전 2026-07-16      매수 12종목  /  매도 8종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 290억   ·   현금 1억(0.4%)      오늘 2026-07-24  vs  5일전 2026-07-16      매수 12종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B45" s="4" t="n"/>
@@ -2005,11 +2005,11 @@
         <v>485</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>131221600</v>
+        <v>128272800</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.48%</t>
+          <t>0.00%→0.44%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -2026,11 +2026,11 @@
         <v>-139</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-38347320</v>
+        <v>-42414460</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>2.77%→2.60%</t>
+          <t>2.90%→2.72%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
@@ -2049,11 +2049,11 @@
         <v>91</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>50210160</v>
+        <v>55051360</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>6.77%→6.87%</t>
+          <t>7.02%→7.13%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -2070,11 +2070,11 @@
         <v>-108</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-54008640</v>
+        <v>-62216640</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>1.05%→0.85%</t>
+          <t>1.15%→0.92%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
@@ -2093,11 +2093,11 @@
         <v>45</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>72504000</v>
+        <v>72846000</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>3.12%→3.35%</t>
+          <t>2.97%→3.19%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -2114,11 +2114,11 @@
         <v>-73</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-77061720</v>
+        <v>-83941240</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>1.64%→1.34%</t>
+          <t>1.69%→1.38%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
@@ -2137,11 +2137,11 @@
         <v>38</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>77976000</v>
+        <v>81874800</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>5.82%→6.03%</t>
+          <t>5.78%→6.00%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
@@ -2158,11 +2158,11 @@
         <v>-38</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-104690000</v>
+        <v>-122740000</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>7.39%→6.92%</t>
+          <t>8.19%→7.68%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
@@ -2181,11 +2181,11 @@
         <v>33</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>118377600</v>
+        <v>131670000</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>0.43%→0.86%</t>
+          <t>0.46%→0.91%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -2202,11 +2202,11 @@
         <v>-18</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-65595600</v>
+        <v>-63475200</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>1.43%→1.18%</t>
+          <t>1.31%→1.08%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
@@ -2225,11 +2225,11 @@
         <v>26</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>35587760</v>
+        <v>38077520</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>0.32%→0.44%</t>
+          <t>0.32%→0.45%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -2246,11 +2246,11 @@
         <v>-10</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-67184000</v>
+        <v>-66196000</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>1.28%→1.02%</t>
+          <t>1.20%→0.96%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
@@ -2269,11 +2269,11 @@
         <v>25</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>56145000</v>
+        <v>61750000</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>2.80%→2.98%</t>
+          <t>2.92%→3.10%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -2290,11 +2290,11 @@
         <v>-9</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-70452000</v>
+        <v>-77839200</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>0.26%→0.00%</t>
+          <t>0.27%→0.00%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
@@ -2313,11 +2313,11 @@
         <v>18</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>85636800</v>
+        <v>94392000</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>2.29%→2.57%</t>
+          <t>2.39%→2.69%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -2334,11 +2334,11 @@
         <v>-5</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-49704000</v>
+        <v>-49438000</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>1.31%→1.12%</t>
+          <t>1.24%→1.05%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
@@ -2357,11 +2357,11 @@
         <v>15</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>93594000</v>
+        <v>93024000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>3.23%→3.53%</t>
+          <t>3.04%→3.32%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
@@ -2385,11 +2385,11 @@
         <v>6</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>44505600</v>
+        <v>44824800</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>1.99%→2.13%</t>
+          <t>1.89%→2.03%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -2413,11 +2413,11 @@
         <v>5</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>59470000</v>
+        <v>58558000</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>2.93%→3.11%</t>
+          <t>2.73%→2.90%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
@@ -2441,11 +2441,11 @@
         <v>4</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>33956800</v>
+        <v>34443200</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>2.65%→2.74%</t>
+          <t>2.54%→2.63%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
@@ -2462,7 +2462,7 @@
     <row r="61" ht="19" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 456억   ·   현금 15억(2.9%)      오늘 2026-07-24  vs  5일전 2026-07-16      매수 2종목  /  매도 5종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 484억   ·   현금 15억(2.9%)      오늘 2026-07-24  vs  5일전 2026-07-16      매수 2종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B61" s="4" t="n"/>
@@ -2558,7 +2558,7 @@
         <v>38</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>732883200</v>
+        <v>726339600</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>-93</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-219256800</v>
+        <v>-217299150</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>36</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>1451520000</v>
+        <v>1438560000</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>-32</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-266291200</v>
+        <v>-263913600</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>-22</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-250588800</v>
+        <v>-248351400</v>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>-15</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-191184000</v>
+        <v>-189477000</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>-8</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-274624000</v>
+        <v>-272172000</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>

--- a/reports/pdf_rolling5_20260724.xlsx
+++ b/reports/pdf_rolling5_20260724.xlsx
@@ -927,111 +927,111 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>406931400</v>
+        <v>1171342800</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>0.50%→0.61%</t>
+          <t>4.17%→4.03%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>66→78</t>
+          <t>168→180</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>노바렉스</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-539199000</v>
+        <v>-258974400</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>0.27%→0.19%</t>
+          <t>0.30%→0.26%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>51→31</t>
+          <t>108→88</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>428976000</v>
+        <v>406931400</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>0.67%→0.77%</t>
+          <t>0.50%→0.61%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>82→94</t>
+          <t>66→78</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>노바렉스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-258974400</v>
+        <v>-539199000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>0.30%→0.26%</t>
+          <t>0.27%→0.19%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>108→88</t>
+          <t>51→31</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1171342800</v>
+        <v>428976000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>4.17%→4.03%</t>
+          <t>0.67%→0.77%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>168→180</t>
+          <t>82→94</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1124,23 +1124,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>오스코텍</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-433742400</v>
+        <v>-421230600</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.89%→0.91%</t>
+          <t>0.56%→0.48%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>142→128</t>
+          <t>84→70</t>
         </is>
       </c>
     </row>
@@ -1168,23 +1168,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>오스코텍</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-421230600</v>
+        <v>-433742400</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.56%→0.48%</t>
+          <t>0.89%→0.91%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>84→70</t>
+          <t>142→128</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260724.xlsx
+++ b/reports/pdf_rolling5_20260724.xlsx
@@ -927,44 +927,44 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1171342800</v>
+        <v>428976000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>4.17%→4.03%</t>
+          <t>0.67%→0.77%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>168→180</t>
+          <t>82→94</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>노바렉스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-258974400</v>
+        <v>-539199000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>0.30%→0.26%</t>
+          <t>0.27%→0.19%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>108→88</t>
+          <t>51→31</t>
         </is>
       </c>
     </row>
@@ -992,46 +992,46 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>노바렉스</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-539199000</v>
+        <v>-258974400</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>0.27%→0.19%</t>
+          <t>0.30%→0.26%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>51→31</t>
+          <t>108→88</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>428976000</v>
+        <v>1171342800</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>0.67%→0.77%</t>
+          <t>4.17%→4.03%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>82→94</t>
+          <t>168→180</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1124,23 +1124,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>오스코텍</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-421230600</v>
+        <v>-433742400</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.56%→0.48%</t>
+          <t>0.89%→0.91%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>84→70</t>
+          <t>142→128</t>
         </is>
       </c>
     </row>
@@ -1168,23 +1168,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>오스코텍</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-433742400</v>
+        <v>-394816800</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.89%→0.91%</t>
+          <t>0.37%→0.27%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>142→128</t>
+          <t>56→42</t>
         </is>
       </c>
     </row>
@@ -1212,23 +1212,23 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-394816800</v>
+        <v>-421230600</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.37%→0.27%</t>
+          <t>0.56%→0.48%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>56→42</t>
+          <t>84→70</t>
         </is>
       </c>
     </row>
@@ -1284,23 +1284,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-381312000</v>
+        <v>-442679400</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>1.24%→1.08%</t>
+          <t>2.23%→2.23%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>138→132</t>
         </is>
       </c>
     </row>
@@ -1312,23 +1312,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-442679400</v>
+        <v>-381312000</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>2.23%→2.23%</t>
+          <t>1.24%→1.08%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>138→132</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>
@@ -1746,23 +1746,23 @@
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-2278210000</v>
+        <v>-2141990000</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>7.61%→5.92%</t>
+          <t>9.85%→7.28%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>150→130</t>
+          <t>190→170</t>
         </is>
       </c>
     </row>
@@ -1834,23 +1834,23 @@
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H39" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-2141990000</v>
+        <v>-2278210000</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>9.85%→7.28%</t>
+          <t>7.61%→5.92%</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
         <is>
-          <t>190→170</t>
+          <t>150→130</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260724.xlsx
+++ b/reports/pdf_rolling5_20260724.xlsx
@@ -927,23 +927,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>428976000</v>
+        <v>406931400</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>0.67%→0.77%</t>
+          <t>0.50%→0.61%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>82→94</t>
+          <t>66→78</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -971,23 +971,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>406931400</v>
+        <v>428976000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>0.50%→0.61%</t>
+          <t>0.67%→0.77%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>66→78</t>
+          <t>82→94</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -1124,23 +1124,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>오스코텍</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-433742400</v>
+        <v>-394816800</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.89%→0.91%</t>
+          <t>0.37%→0.27%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>142→128</t>
+          <t>56→42</t>
         </is>
       </c>
     </row>
@@ -1168,23 +1168,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>오스코텍</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-394816800</v>
+        <v>-433742400</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.37%→0.27%</t>
+          <t>0.89%→0.91%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>56→42</t>
+          <t>142→128</t>
         </is>
       </c>
     </row>
@@ -1284,23 +1284,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-442679400</v>
+        <v>-381312000</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>2.23%→2.23%</t>
+          <t>1.24%→1.08%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>138→132</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>
@@ -1312,23 +1312,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-381312000</v>
+        <v>-442679400</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>1.24%→1.08%</t>
+          <t>2.23%→2.23%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>138→132</t>
         </is>
       </c>
     </row>
@@ -1746,23 +1746,23 @@
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-2141990000</v>
+        <v>-2278210000</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>9.85%→7.28%</t>
+          <t>7.61%→5.92%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>190→170</t>
+          <t>150→130</t>
         </is>
       </c>
     </row>
@@ -1834,23 +1834,23 @@
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H39" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-2278210000</v>
+        <v>-2141990000</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>7.61%→5.92%</t>
+          <t>9.85%→7.28%</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
         <is>
-          <t>150→130</t>
+          <t>190→170</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260724.xlsx
+++ b/reports/pdf_rolling5_20260724.xlsx
@@ -927,111 +927,111 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>406931400</v>
+        <v>1171342800</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>0.50%→0.61%</t>
+          <t>4.17%→4.03%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>66→78</t>
+          <t>168→180</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>노바렉스</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-539199000</v>
+        <v>-258974400</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>0.27%→0.19%</t>
+          <t>0.30%→0.26%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>51→31</t>
+          <t>108→88</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>428976000</v>
+        <v>406931400</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>0.67%→0.77%</t>
+          <t>0.50%→0.61%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>82→94</t>
+          <t>66→78</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>노바렉스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-258974400</v>
+        <v>-539199000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>0.30%→0.26%</t>
+          <t>0.27%→0.19%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>108→88</t>
+          <t>51→31</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1171342800</v>
+        <v>428976000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>4.17%→4.03%</t>
+          <t>0.67%→0.77%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>168→180</t>
+          <t>82→94</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1124,23 +1124,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>오스코텍</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-394816800</v>
+        <v>-433742400</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.37%→0.27%</t>
+          <t>0.89%→0.91%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>56→42</t>
+          <t>142→128</t>
         </is>
       </c>
     </row>
@@ -1168,23 +1168,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>오스코텍</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-433742400</v>
+        <v>-421230600</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.89%→0.91%</t>
+          <t>0.56%→0.48%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>142→128</t>
+          <t>84→70</t>
         </is>
       </c>
     </row>
@@ -1212,23 +1212,23 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-421230600</v>
+        <v>-394816800</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.56%→0.48%</t>
+          <t>0.37%→0.27%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>84→70</t>
+          <t>56→42</t>
         </is>
       </c>
     </row>
@@ -1746,23 +1746,23 @@
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-2278210000</v>
+        <v>-2141990000</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>7.61%→5.92%</t>
+          <t>9.85%→7.28%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>150→130</t>
+          <t>190→170</t>
         </is>
       </c>
     </row>
@@ -1834,23 +1834,23 @@
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H39" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-2141990000</v>
+        <v>-2278210000</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>9.85%→7.28%</t>
+          <t>7.61%→5.92%</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
         <is>
-          <t>190→170</t>
+          <t>150→130</t>
         </is>
       </c>
     </row>
